--- a/etf_holdings/2026-10-08_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-08_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:21</t>
+          <t>2026-10-08 23:45:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0%2585</t>
+          <t>-1.35%2550</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.35%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2585</v>
+        <v>2550</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.54%1,544,000</t>
+          <t>7.62%1,544,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.54%</t>
+          <t>7.62%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:21</t>
+          <t>2026-10-08 23:45:17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-1.73%4835</t>
+          <t>-3%4690</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4835</v>
+        <v>4690</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.84%736,000</t>
+          <t>6.80%736,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.84%</t>
+          <t>6.80%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:21</t>
+          <t>2026-10-08 23:45:17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.68%588</t>
+          <t>-1.19%581</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.38%5,709,000</t>
+          <t>6.41%5,709,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>6.41%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:21</t>
+          <t>2026-10-08 23:45:17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-1.01%787</t>
+          <t>-1.14%778</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-1.01%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>787</v>
+        <v>778</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.62%3,745,000</t>
+          <t>5.63%3,745,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.62%</t>
+          <t>5.63%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:21</t>
+          <t>2026-10-08 23:45:17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-10%11790</t>
+          <t>0%2240</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>11790</v>
+        <v>2240</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.43%179,000</t>
+          <t>4.35%1,016,225</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.43%</t>
+          <t>4.35%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>179000</v>
+        <v>1016225</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:21</t>
+          <t>2026-10-08 23:45:17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-2.18%2240</t>
+          <t>-9.97%10615</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-2.18%</t>
+          <t>-9.97%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2240</v>
+        <v>10615</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.40%1,016,225</t>
+          <t>4.03%179,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.40%</t>
+          <t>4.03%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1016225</v>
+        <v>179000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:21</t>
+          <t>2026-10-08 23:45:17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-4.31%1000</t>
+          <t>-2%980</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-4.31%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.15%2,101,000</t>
+          <t>4.01%2,101,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.15%</t>
+          <t>4.01%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:21</t>
+          <t>2026-10-08 23:45:17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.58%1705</t>
+          <t>-2.92%2330</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.58%</t>
+          <t>-2.92%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1705</v>
+        <v>2330</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.82%1,180,000</t>
+          <t>3.87%845,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.82%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1180000</v>
+        <v>845000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:21</t>
+          <t>2026-10-08 23:45:17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+2.13%2400</t>
+          <t>-1.17%1685</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+2.13%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2400</v>
+        <v>1685</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.75%845,000</t>
+          <t>3.84%1,180,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>3.84%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>845000</v>
+        <v>1180000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:21</t>
+          <t>2026-10-08 23:45:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.75%5950</t>
+          <t>-0.5%592</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5950</v>
+        <v>592</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.50%309,000</t>
+          <t>3.59%3,158,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.59%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>309000</v>
+        <v>3158000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:21</t>
+          <t>2026-10-08 23:45:17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+3.66%595</t>
+          <t>+0.84%6000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+3.66%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>595</v>
+        <v>6000</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.42%3,158,000</t>
+          <t>3.51%309,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.42%</t>
+          <t>3.51%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>3158000</v>
+        <v>309000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:21</t>
+          <t>2026-10-08 23:45:17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.15%6845</t>
+          <t>-2.7%6660</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6845</v>
+        <v>6660</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.25%251,000</t>
+          <t>3.28%251,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>3.28%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:21</t>
+          <t>2026-10-08 23:45:17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-2.47%5530</t>
+          <t>+0.81%5575</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-2.47%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5530</v>
+        <v>5575</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.22%301,000</t>
+          <t>3.18%301,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>3.18%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:21</t>
+          <t>2026-10-08 23:45:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-3.8%3545</t>
+          <t>-2.96%3440</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-2.96%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3545</v>
+        <v>3440</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.59%372,000</t>
+          <t>2.52%372,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.52%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:21</t>
+          <t>2026-10-08 23:45:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.83%1215</t>
+          <t>-7%1130</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+0.83%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1215</v>
+        <v>1130</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.46%1,082,000</t>
+          <t>2.51%1,082,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.51%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:22</t>
+          <t>2026-10-08 23:45:19</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+0.33%300</t>
+          <t>-0.83%297.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-0.83%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>300</v>
+        <v>297.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.82%3,216,000</t>
+          <t>1.84%3,216,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:22</t>
+          <t>2026-10-08 23:45:19</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.41%559</t>
+          <t>-0.18%558</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-1.41%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.64%1,529,000</t>
+          <t>1.63%1,529,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:22</t>
+          <t>2026-10-08 23:45:19</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>5483中美晶</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+0.68%148.5</t>
+          <t>-3.35%216.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>-3.35%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>148.5</v>
+        <v>216.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.43%5,116,000</t>
+          <t>1.46%3,415,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>5116000</v>
+        <v>3415000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:22</t>
+          <t>2026-10-08 23:45:19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+1.14%796</t>
+          <t>-0.67%147.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>796</v>
+        <v>147.5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.40%940,000</t>
+          <t>1.45%5,116,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>940000</v>
+        <v>5116000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:22</t>
+          <t>2026-10-08 23:45:19</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5483中美晶</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+4.19%224</t>
+          <t>+1.26%806</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+4.19%</t>
+          <t>+1.26%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>224</v>
+        <v>806</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.39%3,415,000</t>
+          <t>1.43%940,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>3415000</v>
+        <v>940000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:22</t>
+          <t>2026-10-08 23:45:19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,25 +1724,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>3265台星科</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.99%1720</t>
+          <t>+9.91%238.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.99%</t>
+          <t>+9.91%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1720</v>
+        <v>238.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.39%418,000</t>
+          <t>1.39%3,345,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1751,11 +1751,11 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>418000</v>
+        <v>3345000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:22</t>
+          <t>2026-10-08 23:45:19</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-0.68%733</t>
+          <t>+1.16%1740</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>733</v>
+        <v>1740</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.34%964,000</t>
+          <t>1.37%418,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>964000</v>
+        <v>418000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:22</t>
+          <t>2026-10-08 23:45:19</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-2.37%185</t>
+          <t>-0.82%727</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>-0.82%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>185</v>
+        <v>727</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.30%3,638,000</t>
+          <t>1.35%964,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>3638000</v>
+        <v>964000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:22</t>
+          <t>2026-10-08 23:45:19</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,25 +1907,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-6.51%17750</t>
+          <t>+1.89%188.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-6.51%</t>
+          <t>+1.89%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>17750</v>
+        <v>188.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.29%35,900</t>
+          <t>1.29%3,638,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1934,11 +1934,11 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>35900</v>
+        <v>3638000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:22</t>
+          <t>2026-10-08 23:45:19</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3265台星科</t>
+          <t>5425台半</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+9.87%217</t>
+          <t>-3.83%100.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+9.87%</t>
+          <t>-3.83%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>217</v>
+        <v>100.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.25%3,345,000</t>
+          <t>1.27%6,382,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>3345000</v>
+        <v>6382000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:22</t>
+          <t>2026-10-08 23:45:19</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>6214精誠</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-3.82%365.5</t>
+          <t>+1.32%192</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-3.82%</t>
+          <t>+1.32%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>365.5</v>
+        <v>192</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.25%1,737,000</t>
+          <t>1.24%3,438,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1737000</v>
+        <v>3438000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:22</t>
+          <t>2026-10-08 23:45:19</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-1.61%732</t>
+          <t>+1.64%744</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>+1.64%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.23%876,000</t>
+          <t>1.22%876,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:22</t>
+          <t>2026-10-08 23:45:19</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,25 +2151,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6214精誠</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+0.53%189.5</t>
+          <t>-1.49%17485</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>189.5</v>
+        <v>17485</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.22%3,438,000</t>
+          <t>1.22%35,900</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2178,11 +2178,11 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>3438000</v>
+        <v>35900</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:22</t>
+          <t>2026-10-08 23:45:19</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,25 +2212,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5425台半</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+3.98%104.5</t>
+          <t>-0.68%363</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+3.98%</t>
+          <t>-0.68%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>104.5</v>
+        <v>363</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.21%6,382,000</t>
+          <t>1.21%1,737,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2239,11 +2239,11 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>6382000</v>
+        <v>1737000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:22</t>
+          <t>2026-10-08 23:45:19</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,25 +2278,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+2.81%1645</t>
+          <t>+3.95%1710</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+2.81%</t>
+          <t>+3.95%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1645</v>
+        <v>1710</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.15%382,000</t>
+          <t>1.20%382,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:23</t>
+          <t>2026-10-08 23:45:20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3583辛耘</t>
+          <t>2428興勤</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-2.49%743</t>
+          <t>+5.62%282</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-2.49%</t>
+          <t>+5.62%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>743</v>
+        <v>282</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.14%790,000</t>
+          <t>1.16%2,268,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>790000</v>
+        <v>2268000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:23</t>
+          <t>2026-10-08 23:45:20</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,25 +2395,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2428興勤</t>
+          <t>6239力成</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+1.71%267</t>
+          <t>+0.16%308</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+1.71%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>267</v>
+        <v>308</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.12%2,268,000</t>
+          <t>1.12%1,910,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2422,11 +2422,11 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>2268000</v>
+        <v>1910000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:23</t>
+          <t>2026-10-08 23:45:20</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,25 +2456,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6239力成</t>
+          <t>3583辛耘</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-0.97%307.5</t>
+          <t>-0.94%736</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>-0.94%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>307.5</v>
+        <v>736</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.12%1,910,000</t>
+          <t>1.12%790,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1910000</v>
+        <v>790000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:23</t>
+          <t>2026-10-08 23:45:20</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2467志聖</t>
+          <t>2478大毅</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.22%569</t>
+          <t>0%134.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>569</v>
+        <v>134.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.09%1,000,000</t>
+          <t>1.11%4,331,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1000000</v>
+        <v>4331000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:23</t>
+          <t>2026-10-08 23:45:20</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+0.58%174</t>
+          <t>0%174</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.07%3,280,000</t>
+          <t>1.09%3,280,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:23</t>
+          <t>2026-10-08 23:45:20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2478大毅</t>
+          <t>2467志聖</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+4.67%134.5</t>
+          <t>-2.99%552</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+4.67%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>134.5</v>
+        <v>552</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.05%4,331,000</t>
+          <t>1.09%1,000,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>4331000</v>
+        <v>1000000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:23</t>
+          <t>2026-10-08 23:45:20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.65%156</t>
+          <t>-0.96%154.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>156</v>
+        <v>154.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.98%3,344,000</t>
+          <t>1.00%3,344,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:23</t>
+          <t>2026-10-08 23:45:20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,25 +2766,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+5.13%1045</t>
+          <t>-1.44%1030</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+5.13%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1045</v>
+        <v>1030</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.85%455,000</t>
+          <t>0.91%455,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:23</t>
+          <t>2026-10-08 23:45:20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+2.76%428</t>
+          <t>-1.64%421</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+2.76%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.81%1,032,000</t>
+          <t>0.84%1,032,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:23</t>
+          <t>2026-10-08 23:45:20</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,25 +2888,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-0.41%240</t>
+          <t>-0.62%238.5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>240</v>
+        <v>238.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.73%1,607,000</t>
+          <t>0.74%1,607,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.74%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:23</t>
+          <t>2026-10-08 23:45:20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+9.9%505</t>
+          <t>+9.9%555</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2958,24 +2958,24 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>505</v>
+        <v>555</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.46%527,000</t>
+          <t>0.68%706,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>527000</v>
+        <v>706000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:23</t>
+          <t>2026-10-08 23:45:20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,25 +3010,25 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+1.06%670</t>
+          <t>+0.6%674</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+1.06%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.38%304,000</t>
+          <t>0.39%304,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:23</t>
+          <t>2026-10-08 23:45:20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,25 +3071,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+0.98%51.5</t>
+          <t>-1.94%50.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+0.98%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>51.5</v>
+        <v>50.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.36%3,712,000</t>
+          <t>0.37%3,712,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:23</t>
+          <t>2026-10-08 23:45:20</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0%131.5</t>
+          <t>-0.76%130.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.76%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>131.5</v>
+        <v>130.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:23</t>
+          <t>2026-10-08 23:45:20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,38 +3188,38 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6640均華</t>
+          <t>2885元大金</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-4.85%1080</t>
+          <t>-2.43%68.3</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-4.85%</t>
+          <t>-2.43%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1080</v>
+        <v>68.3</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.31%143,000</t>
+          <t>0.30%2,213,556</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>143000</v>
+        <v>2213556</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:25</t>
+          <t>2026-10-08 23:45:21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,34 +3249,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3529力旺</t>
+          <t>6640均華</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-3.21%3015</t>
+          <t>-2.78%1050</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-3.21%</t>
+          <t>-2.78%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>3015</v>
+        <v>1050</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.30%51,000</t>
+          <t>0.29%143,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>51000</v>
+        <v>143000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:25</t>
+          <t>2026-10-08 23:45:21</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+0.2%245.5</t>
+          <t>-1.63%241.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>245.5</v>
+        <v>241.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:25</t>
+          <t>2026-10-08 23:45:21</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,38 +3371,38 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2885元大金</t>
+          <t>6446藥華藥</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+1.01%70</t>
+          <t>-0.83%1195</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>-0.83%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>70</v>
+        <v>1195</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.29%2,213,556</t>
+          <t>0.10%42,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>2213556</v>
+        <v>42000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:25</t>
+          <t>2026-10-08 23:45:21</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,34 +3432,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6446藥華藥</t>
+          <t>6177達麗</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+2.55%1205</t>
+          <t>+0.11%45.95</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+2.55%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1205</v>
+        <v>45.95</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.09%42,000</t>
+          <t>0.02%194,350</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.02%</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>42000</v>
+        <v>194350</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:25</t>
+          <t>2026-10-08 23:45:21</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,25 +3493,25 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>6177達麗</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+1.66%45.9</t>
+          <t>-1.18%8360</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+1.66%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>45.9</v>
+        <v>8360</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.02%194,350</t>
+          <t>0.02%1,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3520,11 +3520,11 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>194350</v>
+        <v>1000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:25</t>
+          <t>2026-10-08 23:45:21</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3554,30 +3554,30 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>3529力旺</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>+1.01%8460</t>
+          <t>-3.32%2915</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>-3.32%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>8460</v>
+        <v>2915</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0.02%1,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:25</t>
+          <t>2026-10-08 23:45:21</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3620,16 +3620,16 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>+0.88%171</t>
+          <t>+0.29%171.5</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>171</v>
+        <v>171.5</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:25</t>
+          <t>2026-10-08 23:45:21</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3681,16 +3681,16 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-0.36%549</t>
+          <t>-2.55%535</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>-2.55%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:25</t>
+          <t>2026-10-08 23:45:21</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3742,16 +3742,16 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>+0.86%702</t>
+          <t>-1.42%692</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>-1.42%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:25</t>
+          <t>2026-10-08 23:45:21</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3803,16 +3803,16 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>+1.01%49.8</t>
+          <t>-1%49.3</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>49.8</v>
+        <v>49.3</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:25</t>
+          <t>2026-10-08 23:45:21</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3864,16 +3864,16 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>+0.65%155.5</t>
+          <t>-1.61%153</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>155.5</v>
+        <v>153</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-08_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-08_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:17</t>
+          <t>2026-10-08 23:52:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:17</t>
+          <t>2026-10-08 23:52:47</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:17</t>
+          <t>2026-10-08 23:52:47</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:17</t>
+          <t>2026-10-08 23:52:47</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:17</t>
+          <t>2026-10-08 23:52:47</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:17</t>
+          <t>2026-10-08 23:52:47</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:17</t>
+          <t>2026-10-08 23:52:47</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:17</t>
+          <t>2026-10-08 23:52:47</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:17</t>
+          <t>2026-10-08 23:52:47</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:17</t>
+          <t>2026-10-08 23:52:47</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:17</t>
+          <t>2026-10-08 23:52:47</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:17</t>
+          <t>2026-10-08 23:52:47</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:17</t>
+          <t>2026-10-08 23:52:47</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:17</t>
+          <t>2026-10-08 23:52:47</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:17</t>
+          <t>2026-10-08 23:52:47</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:19</t>
+          <t>2026-10-08 23:52:48</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:19</t>
+          <t>2026-10-08 23:52:48</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:19</t>
+          <t>2026-10-08 23:52:48</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:19</t>
+          <t>2026-10-08 23:52:48</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:19</t>
+          <t>2026-10-08 23:52:48</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:19</t>
+          <t>2026-10-08 23:52:48</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:19</t>
+          <t>2026-10-08 23:52:48</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:19</t>
+          <t>2026-10-08 23:52:48</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:19</t>
+          <t>2026-10-08 23:52:48</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:19</t>
+          <t>2026-10-08 23:52:48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:19</t>
+          <t>2026-10-08 23:52:48</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:19</t>
+          <t>2026-10-08 23:52:48</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:19</t>
+          <t>2026-10-08 23:52:48</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:19</t>
+          <t>2026-10-08 23:52:48</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:19</t>
+          <t>2026-10-08 23:52:48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:20</t>
+          <t>2026-10-08 23:52:50</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:20</t>
+          <t>2026-10-08 23:52:50</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:20</t>
+          <t>2026-10-08 23:52:50</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:20</t>
+          <t>2026-10-08 23:52:50</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:20</t>
+          <t>2026-10-08 23:52:50</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:20</t>
+          <t>2026-10-08 23:52:50</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:20</t>
+          <t>2026-10-08 23:52:50</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:20</t>
+          <t>2026-10-08 23:52:50</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:20</t>
+          <t>2026-10-08 23:52:50</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:20</t>
+          <t>2026-10-08 23:52:50</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:20</t>
+          <t>2026-10-08 23:52:50</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:20</t>
+          <t>2026-10-08 23:52:50</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:20</t>
+          <t>2026-10-08 23:52:50</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:20</t>
+          <t>2026-10-08 23:52:50</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:20</t>
+          <t>2026-10-08 23:52:50</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:21</t>
+          <t>2026-10-08 23:52:51</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:21</t>
+          <t>2026-10-08 23:52:51</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:21</t>
+          <t>2026-10-08 23:52:51</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:21</t>
+          <t>2026-10-08 23:52:51</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:21</t>
+          <t>2026-10-08 23:52:51</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:21</t>
+          <t>2026-10-08 23:52:51</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:21</t>
+          <t>2026-10-08 23:52:51</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:21</t>
+          <t>2026-10-08 23:52:51</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:21</t>
+          <t>2026-10-08 23:52:51</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:21</t>
+          <t>2026-10-08 23:52:51</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-08 23:45:21</t>
+          <t>2026-10-08 23:52:51</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
